--- a/ips/pmtpc4/vplan/pmtpc4_testplan.xlsx
+++ b/ips/pmtpc4/vplan/pmtpc4_testplan.xlsx
@@ -3147,7 +3147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>40/40 runs passed</t>
+          <t>41/41 runs passed</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -3279,63 +3279,63 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>93.5% (458/490 bits); 100.0% net of documented constant nets</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>reports/_cov/code_report/ (DUT-scoped)</t>
+          <t>reports/_cov/toggle_summary.txt (toggle build: no bind/dump top; bit-weighted over DUT RTL)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Register-bit toggle (RAL-derived)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>100.0% (486/486 bit-directions)</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>reports/_cov/reg_bit_toggle.txt</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Code-coverage waivers (module scoping)</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Code-coverage exclusions</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>module -apb_fsm_cov*</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>code scoping</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>module -apb_if*</t>
+          <t>module -apb_fsm_cov*</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -3347,12 +3347,12 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>module -apb_pkg*</t>
+          <t>module -apb_if*</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -3364,12 +3364,12 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>module -drv_cb*</t>
+          <t>module -apb_pkg*</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -3381,12 +3381,12 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>module -mon_cb*</t>
+          <t>module -drv_cb*</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -3398,12 +3398,12 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>module -pmtpc4_apb_sva*</t>
+          <t>module -mon_cb*</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -3415,12 +3415,12 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>module -pmtpc4_channel_sva*</t>
+          <t>module -pmtpc4_apb_sva*</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -3432,12 +3432,12 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>module -pmtpc4_presc_sva*</t>
+          <t>module -pmtpc4_binds*</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -3449,12 +3449,12 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>module -pmtpc4_pwm_cov*</t>
+          <t>module -pmtpc4_channel_sva*</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -3466,12 +3466,12 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>module -pmtpc4_ral_pkg*</t>
+          <t>module -pmtpc4_dump*</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -3483,12 +3483,12 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>module -pmtpc4_tb_top*</t>
+          <t>module -pmtpc4_presc_sva*</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -3500,12 +3500,12 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>module -pmtpc4_test_pkg*</t>
+          <t>module -pmtpc4_pwm_cov*</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -3517,12 +3517,12 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>module -pmtpc4_top_sva*</t>
+          <t>module -pmtpc4_ral_pkg*</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -3534,12 +3534,12 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>module -pwm_if*</t>
+          <t>module -pmtpc4_tb_top*</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -3551,12 +3551,12 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>module -pwm_pkg*</t>
+          <t>module -pmtpc4_test_pkg*</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -3568,12 +3568,12 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>module -reset_if*</t>
+          <t>module -pmtpc4_top_sva*</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -3585,12 +3585,12 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>module -uvm_pkg</t>
+          <t>module -pwm_if*</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -3602,12 +3602,12 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>module -pmtpc4_prescaler</t>
+          <t>module -pwm_pkg*</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -3619,12 +3619,12 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>signal -cpuif_wr_biten</t>
+          <t>module -reset_if*</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -3636,12 +3636,12 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>signal -cpuif_req_stall_wr</t>
+          <t>module -uvm_pkg</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>DUT scoping (all code metrics)</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -3653,340 +3653,68 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>signal -cpuif_req_stall_rd</t>
+          <t>module -pmtpc4_regblock</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>toggle-only waiver</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
+          <t>dv/pmtpc4_toggle_waivers.txt</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>signal -cpuif_rd_err</t>
+          <t>module -pmtpc4_regblock_pkg*</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>toggle-only waiver</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
+          <t>dv/pmtpc4_toggle_waivers.txt</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>signal -cpuif_wr_err</t>
+          <t>signal -pmtpc4_tb_top.dut.cpuif_wr_biten</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>toggle-only waiver</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
+          <t>dv/pmtpc4_toggle_waivers.txt</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>signal -decoded_err</t>
+          <t>signal -pmtpc4_tb_top.dut.cpuif_rd_data_pad</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>code scoping</t>
+          <t>toggle-only waiver</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>signal -is_valid_addr</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>code scoping</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>signal -is_valid_rw</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>code scoping</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>signal -readback_err</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>code scoping</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>signal -cnt</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>code scoping</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>signal -tick_en</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>code scoping</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>signal -next_c</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>code scoping</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>signal -load_next_c</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>code scoping</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>signal -cpuif_addr</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>code scoping</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>signal -decoded_wr_biten</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>code scoping</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>signal -readback_data_var</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>code scoping</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>signal -start_trig</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>code scoping</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>signal -pwm_level</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>code scoping</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>signal -int_status_val</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>code scoping</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>signal -int_en_val</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>code scoping</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>signal -compare_shadow</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>code scoping</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>signal -cpuif_rd_data_pad</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>code scoping</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
+          <t>dv/pmtpc4_toggle_waivers.txt</t>
         </is>
       </c>
     </row>

--- a/ips/pmtpc4/vplan/pmtpc4_testplan.xlsx
+++ b/ips/pmtpc4/vplan/pmtpc4_testplan.xlsx
@@ -2322,7 +2322,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Static gate (Verible lint / Yosys elaboration)</t>
+          <t>Static gate (Verible lint / xsim elaboration / Vivado synthesis)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Static gate (Verible lint / Yosys elaboration)</t>
+          <t>Static gate (Verible lint / xsim elaboration / Vivado synthesis)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3147,7 +3147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3466,7 +3466,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>module -pmtpc4_dump*</t>
+          <t>module -pmtpc4_presc_sva*</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -3483,7 +3483,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>module -pmtpc4_presc_sva*</t>
+          <t>module -pmtpc4_pwm_cov*</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -3500,7 +3500,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>module -pmtpc4_pwm_cov*</t>
+          <t>module -pmtpc4_ral_pkg*</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -3517,7 +3517,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>module -pmtpc4_ral_pkg*</t>
+          <t>module -pmtpc4_tb_top*</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -3534,7 +3534,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>module -pmtpc4_tb_top*</t>
+          <t>module -pmtpc4_test_pkg*</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>module -pmtpc4_test_pkg*</t>
+          <t>module -pmtpc4_top_sva*</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -3568,7 +3568,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>module -pmtpc4_top_sva*</t>
+          <t>module -pwm_if*</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -3585,7 +3585,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>module -pwm_if*</t>
+          <t>module -pwm_pkg*</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -3602,7 +3602,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>module -pwm_pkg*</t>
+          <t>module -reset_if*</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -3619,7 +3619,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>module -reset_if*</t>
+          <t>module -uvm_pkg</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -3636,17 +3636,17 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>module -uvm_pkg</t>
+          <t>module -pmtpc4_regblock_pkg*</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>DUT scoping (all code metrics)</t>
+          <t>toggle-only waiver</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>dv/pmtpc4_cov_exclusions.txt</t>
+          <t>dv/pmtpc4_toggle_waivers.txt</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>module -pmtpc4_regblock_pkg*</t>
+          <t>signal -pmtpc4_tb_top.dut.cpuif_wr_biten</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -3687,7 +3687,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>signal -pmtpc4_tb_top.dut.cpuif_wr_biten</t>
+          <t>signal -pmtpc4_tb_top.dut.cpuif_rd_data_pad</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -3696,23 +3696,6 @@
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>dv/pmtpc4_toggle_waivers.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>signal -pmtpc4_tb_top.dut.cpuif_rd_data_pad</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>toggle-only waiver</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>dv/pmtpc4_toggle_waivers.txt</t>
         </is>
